--- a/docs/StructureDefinition-LTC-Bundle-Payload.xlsx
+++ b/docs/StructureDefinition-LTC-Bundle-Payload.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTC-Bundle-Payload.xlsx
+++ b/docs/StructureDefinition-LTC-Bundle-Payload.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTC-Bundle-Payload.xlsx
+++ b/docs/StructureDefinition-LTC-Bundle-Payload.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTC-Bundle-Payload.xlsx
+++ b/docs/StructureDefinition-LTC-Bundle-Payload.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
